--- a/public/Excel_Var2_Starter.xlsx
+++ b/public/Excel_Var2_Starter.xlsx
@@ -19,25 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="007A4100"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -52,14 +40,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="12"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00888888"/>
+      <color rgb="00666666"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -69,11 +56,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -88,6 +70,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,44 +104,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,821 +516,713 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A2:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>[INSTRUCTION] MENU — Merge title row. Freeze row 1. AutoFill Item-01 through Item-20. Insert 2 columns (Supplier, Reorder Level). Format Cost/Price as Currency, Margin as %. Conditional formatting (red) for margin &lt; 20%. Name range 'MenuPrices'. Wrap text in Item Description. Convert to Table, apply orange style. Add Total Row. Filter Dinner items. Sort by margin. Remove duplicates. Write SUM, AVERAGE, MAX, MIN, COUNTA, IF, nested IF, COUNTIF, SUMIF, LEFT, TODAY, XLOOKUP, IFERROR formulas.</t>
-        </is>
-      </c>
-    </row>
+    <row r="1" ht="24" customHeight="1"/>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Cactus Kitchen — Inventory &amp; Profit Tracker 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Item Name</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Margin %</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Stock Qty</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Reorder Alert</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Cat Code (MID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Item-01</t>
+        </is>
+      </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Item Name</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Item Description</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Stock Qty</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Reorder Alert</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CK-BF-01</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
           <t>Huevos Rancheros</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Two eggs over easy on crispy corn tortillas with ranchero sauce, black beans, and cotija cheese</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Breakfast</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E3" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F3" s="5" t="n">
         <v>10.99</v>
       </c>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="4" t="n">
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="2" t="n">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>CK-BF-02</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Item-02</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Chilaquiles Verde</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>House-made green tomatillo salsa over crispy tortilla chips, topped with crema and queso fresco</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Breakfast</t>
         </is>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E4" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F4" s="10" t="n">
         <v>9.99</v>
       </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="8" t="n">
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="7" t="n">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CK-BF-03</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="11" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Southwest Omelette</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Three-egg omelette stuffed with roasted peppers, Monterey Jack, and house chorizo</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Breakfast</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E5" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F5" s="5" t="n">
         <v>11.99</v>
       </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="4" t="n">
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="2" t="n">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>CK-LN-01</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Green Chile Burger</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Half-pound beef patty with roasted Hatch green chile, pepper jack cheese, and chipotle aioli</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E6" s="10" t="n">
         <v>5.2</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F6" s="10" t="n">
         <v>14.99</v>
       </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="8" t="n">
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="7" t="n">
         <v>67</v>
       </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>CK-LN-02</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Fish Tacos</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Two beer-battered tilapia tacos with cabbage slaw, pico de gallo, and lime crema</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E7" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F7" s="5" t="n">
         <v>13.99</v>
       </c>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="4" t="n">
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="2" t="n">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>CK-LN-03</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Cactus Garden Salad</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Mixed greens with jicama, pepitas, avocado, queso fresco, and cilantro lime dressing</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E8" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F8" s="10" t="n">
         <v>10.99</v>
       </c>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="8" t="n">
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="7" t="n">
         <v>34</v>
       </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>CK-LN-04</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Sonoran Hot Dog</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Bacon-wrapped hot dog in a bolillo bun with pinto beans, tomato, onion, and jalapeño sauce</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E9" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F9" s="5" t="n">
         <v>11.99</v>
       </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="4" t="n">
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="2" t="n">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>CK-DN-01</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Carne Asada Plate</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Grilled skirt steak marinated in citrus and spices, served with rice, beans, and flour tortillas</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E10" s="10" t="n">
         <v>8.4</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F10" s="10" t="n">
         <v>22.99</v>
       </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n">
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="7" t="n">
         <v>55</v>
       </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>CK-DN-02</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Mole Chicken</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Free-range chicken breast in house-made Oaxacan mole negro with sesame rice pilaf</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E11" s="5" t="n">
         <v>7.2</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F11" s="5" t="n">
         <v>19.99</v>
       </c>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="4" t="n">
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="2" t="n">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>CK-DN-03</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Tamale Platter</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Three handmade masa tamales with red chile pork, topped with queso and jalapeño crema</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E12" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F12" s="10" t="n">
         <v>18.99</v>
       </c>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n">
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="7" t="n">
         <v>37</v>
       </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>CK-DN-04</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Enchiladas Verdes</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Three corn tortilla enchiladas filled with roasted chicken in tomatillo sauce with sour cream</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Three corn tortilla enchiladas filled with roasted chicken in tomatillo sauce</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E13" s="5" t="n">
         <v>5.9</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F13" s="5" t="n">
         <v>16.99</v>
       </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="4" t="n">
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="2" t="n">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>CK-DN-05</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ribeye Fajitas</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>12 oz ribeye fajitas with sautéed peppers and onions, served with warm tortillas and sides</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E14" s="10" t="n">
         <v>11.2</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F14" s="10" t="n">
         <v>28.99</v>
       </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="8" t="n">
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="7" t="n">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>CK-DN-06</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Seafood Cazuela</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Gulf shrimp and sea scallops in a spiced tomato broth with chorizo and crusty bread</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E15" s="5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F15" s="5" t="n">
         <v>25.99</v>
       </c>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="4" t="n">
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="2" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>CK-SD-01</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Elote Street Corn</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Grilled corn on the cob with mayo, cotija cheese, chile powder, and fresh lime</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E16" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F16" s="10" t="n">
         <v>4.99</v>
       </c>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8" t="n">
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="7" t="n">
         <v>82</v>
       </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>CK-SD-02</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Black Bean Soup</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Slow-simmered black beans with epazote, topped with crema and pickled red onion</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E17" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F17" s="5" t="n">
         <v>5.99</v>
       </c>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="4" t="n">
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="2" t="n">
         <v>64</v>
       </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>CK-DS-01</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Churros con Chocolate</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Fresh-fried churros dusted with cinnamon sugar, served with rich Mexican hot chocolate dipping sauce</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Fresh-fried churros dusted with cinnamon sugar, served with Mexican hot chocolate dipping sauce</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Desserts</t>
         </is>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E18" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F18" s="10" t="n">
         <v>7.99</v>
       </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8" t="n">
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="7" t="n">
         <v>56</v>
       </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>CK-DS-02</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Tres Leches Cake</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Light sponge cake soaked in three milks, topped with fresh whipped cream and mango coulis</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Desserts</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E19" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F19" s="5" t="n">
         <v>8.99</v>
       </c>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="4" t="n">
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="2" t="n">
         <v>44</v>
       </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>CK-BV-01</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Horchata</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>House-made rice and almond drink with cinnamon and vanilla, served over ice</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Beverages</t>
         </is>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E20" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F20" s="10" t="n">
         <v>3.99</v>
       </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8" t="n">
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="7" t="n">
         <v>90</v>
       </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>CK-BV-02</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Agua de Jamaica</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Chilled hibiscus flower agua fresca lightly sweetened with cane sugar</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Beverages</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E21" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F21" s="5" t="n">
         <v>3.49</v>
       </c>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="4" t="n">
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="2" t="n">
         <v>88</v>
       </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>CK-DN-01</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Queso Fundido</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Melted Oaxacan cheese with chorizo and roasted peppers, served with warm flour tortillas</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Appetizers</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="12" t="n"/>
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Carne Asada Plate</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Grilled skirt steak marinated in citrus and spices, served with rice, beans, and flour tortillas</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="16" t="n">
         <v>8.4</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="16" t="n">
         <v>22.99</v>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="n">
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="15" t="n">
         <v>55</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>SUMMARY FORMULAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Total Revenue if all sold (SUM MenuPrices)</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Average Menu Price (AVERAGE)</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Highest Price Item (MAX)</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Lowest Price Item (MIN)</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Total Menu Items (COUNTA)</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>High Margin IF &gt;=30% (IF) — in Margin col</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Reorder Alert nested IF — col I</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Count by Category (COUNTIF) — Dinner</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Total Revenue by Category (SUMIF) — Dinner</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Category Code LEFT 2 chars — in new col</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Inventory Date (TODAY)</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="inlineStr"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A25:I25"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1345,340 +1233,270 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Supplier Reference Table</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Supplier Reference Table — use for XLOOKUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Supplier Name</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Lead Time</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>CK-BF-01</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Item-01</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Desert Egg Farms</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>farms@desertegg.com</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>2 days</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>CK-BF-02</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Item-02</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Southwest Produce Co.</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>orders@swproduce.com</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>1 day</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>CK-BF-03</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Item-03</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Nevada Dairy Supply</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>supply@nvdairy.com</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>2 days</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>CK-LN-01</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Item-04</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Mojave Meats</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>orders@mojavemeats.com</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>3 days</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>CK-LN-02</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Item-05</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Pacific Seafood NV</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>nv@pacificseafood.com</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>2 days</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>CK-DN-01</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Item-06</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Southwest Produce Co.</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>1 day</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Item-07</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Southwest Produce Co.</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>1 day</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Item-08</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Mojave Meats</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>orders@mojavemeats.com</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>3 days</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>CK-DN-02</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Item-09</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Nevada Valley Poultry</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>orders@nvpoultry.com</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>2 days</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>CK-DN-03</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Item-10</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Southwest Produce Co.</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>orders@swproduce.com</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>1 day</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>CK-DN-05</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Item-12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Mojave Meats</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>orders@mojavemeats.com</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>3 days</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>CK-DN-06</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Item-13</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Pacific Seafood NV</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>nv@pacificseafood.com</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>2 days</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>CK-SD-01</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Southwest Produce Co.</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>orders@swproduce.com</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>1 day</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>CK-BV-01</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Item-18</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Nevada Dairy Supply</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>supply@nvdairy.com</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>2 days</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>CK-BV-02</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Southwest Produce Co.</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>orders@swproduce.com</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>1 day</t>
-        </is>
-      </c>
-    </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>[Students use XLOOKUP to pull Supplier Name from this table into Menu sheet]</t>
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Note: Items 11, 14, 15, 16, 17, 19, 20 have no supplier — IFERROR will show 'No Supplier' for these (intentional).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A17:C17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1694,223 +1512,223 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>[INSTRUCTION] MONTHLY SALES — Plain sales data by category. Use for SUMIF formulas and chart creation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Monthly Sales by Category — use for SUMIF formulas and charts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Breakfast</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Sides</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Desserts</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Beverages</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n">
+      <c r="B3" s="5" t="n">
         <v>4200</v>
       </c>
-      <c r="C3" s="18" t="n">
+      <c r="C3" s="5" t="n">
         <v>6800</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="5" t="n">
         <v>11200</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="5" t="n">
         <v>1800</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="5" t="n">
         <v>2100</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="5" t="n">
         <v>900</v>
       </c>
-      <c r="H3" s="13" t="inlineStr"/>
+      <c r="H3" s="19" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="10" t="n">
         <v>3900</v>
       </c>
-      <c r="C4" s="18" t="n">
+      <c r="C4" s="10" t="n">
         <v>6200</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="10" t="n">
         <v>10800</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="10" t="n">
         <v>1650</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="10" t="n">
         <v>1950</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="10" t="n">
         <v>840</v>
       </c>
-      <c r="H4" s="13" t="inlineStr"/>
+      <c r="H4" s="19" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="5" t="n">
         <v>4500</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="5" t="n">
         <v>7100</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="5" t="n">
         <v>12400</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="5" t="n">
         <v>1950</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="5" t="n">
         <v>2300</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="5" t="n">
         <v>960</v>
       </c>
-      <c r="H5" s="13" t="inlineStr"/>
+      <c r="H5" s="19" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="10" t="n">
         <v>4800</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="10" t="n">
         <v>7600</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="10" t="n">
         <v>13100</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="10" t="n">
         <v>2100</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="10" t="n">
         <v>2450</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="10" t="n">
         <v>1020</v>
       </c>
-      <c r="H6" s="13" t="inlineStr"/>
+      <c r="H6" s="19" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="5" t="n">
         <v>5100</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="5" t="n">
         <v>8200</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="5" t="n">
         <v>14200</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="5" t="n">
         <v>2250</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="5" t="n">
         <v>2600</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="5" t="n">
         <v>1080</v>
       </c>
-      <c r="H7" s="13" t="inlineStr"/>
+      <c r="H7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>June</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="10" t="n">
         <v>5600</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="10" t="n">
         <v>9100</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="10" t="n">
         <v>15800</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="10" t="n">
         <v>2450</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="10" t="n">
         <v>2850</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="10" t="n">
         <v>1180</v>
       </c>
-      <c r="H8" s="13" t="inlineStr"/>
+      <c r="H8" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/Excel_Var2_Starter.xlsx
+++ b/public/Excel_Var2_Starter.xlsx
@@ -338,7 +338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="1">
@@ -414,6 +414,31 @@
           <t>Spend</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Sorted Vendors</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="1">
       <c r="B4" s="2" t="inlineStr">
@@ -457,7 +482,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -482,7 +507,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -507,7 +532,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -532,7 +557,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -557,7 +582,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -577,7 +602,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="1">
@@ -592,7 +617,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
